--- a/docs/assets/reimbursement/Reimbursement.xlsx
+++ b/docs/assets/reimbursement/Reimbursement.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://connectpolyu-my.sharepoint.com/personal/22040929r_connect_polyu_hk/Documents/Research/Sundry/Conference Grant/MobiSys 2025/Reimbursement/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitProject\PolyU-Survival\docs\assets\reimbursement\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="384" documentId="13_ncr:1_{C4FAED3B-86E0-41AA-BD92-D5892802A592}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{899C8111-3E44-4669-B314-0F25ABCAF754}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68F04246-3841-4F71-AC7D-83299B8175DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" firstSheet="2" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6180" yWindow="5030" windowWidth="26670" windowHeight="15460" firstSheet="2" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sample 2" sheetId="2" state="hidden" r:id="rId1"/>
@@ -1198,9 +1198,6 @@
     <t>The HK &amp; Shanghai Banking Corp. Ltd.</t>
   </si>
   <si>
-    <t>004-559599675833</t>
-  </si>
-  <si>
     <t>Anaheim</t>
   </si>
   <si>
@@ -1211,6 +1208,9 @@
   </si>
   <si>
     <t>From hotel to SNA airport</t>
+  </si>
+  <si>
+    <t>004-xxxxxxxxxx</t>
   </si>
 </sst>
 </file>
@@ -2033,7 +2033,7 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="325">
+  <cellXfs count="326">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2644,6 +2644,27 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="2" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="17" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="32" xfId="2" quotePrefix="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2683,12 +2704,6 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2710,20 +2725,26 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="17" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="2" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="17" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="2" fontId="16" fillId="3" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="16" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="16" fillId="3" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="16" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="14" fillId="12" borderId="3" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="14" fillId="12" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="19" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -2746,33 +2767,27 @@
     <xf numFmtId="165" fontId="19" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="16" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="14" fillId="12" borderId="3" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="14" fillId="12" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="16" fillId="3" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="16" fillId="3" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="16" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="19" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="11" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -2788,20 +2803,47 @@
     <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2812,68 +2854,17 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="36" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
     <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="17">
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-    </dxf>
+  <dxfs count="15">
     <dxf>
       <fill>
         <patternFill>
@@ -5965,12 +5956,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A1" s="258" t="s">
+      <c r="A1" s="265" t="s">
         <v>284</v>
       </c>
-      <c r="B1" s="258"/>
-      <c r="C1" s="258"/>
-      <c r="D1" s="258"/>
+      <c r="B1" s="265"/>
+      <c r="C1" s="265"/>
+      <c r="D1" s="265"/>
       <c r="E1" s="240"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
@@ -5989,33 +5980,33 @@
       <c r="A4" s="152" t="s">
         <v>186</v>
       </c>
-      <c r="B4" s="268" t="s">
+      <c r="B4" s="256" t="s">
         <v>187</v>
       </c>
-      <c r="C4" s="268"/>
-      <c r="D4" s="268"/>
+      <c r="C4" s="256"/>
+      <c r="D4" s="256"/>
       <c r="E4" s="222"/>
     </row>
     <row r="5" spans="1:5" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="152" t="s">
         <v>188</v>
       </c>
-      <c r="B5" s="268" t="s">
+      <c r="B5" s="256" t="s">
         <v>189</v>
       </c>
-      <c r="C5" s="268"/>
-      <c r="D5" s="268"/>
+      <c r="C5" s="256"/>
+      <c r="D5" s="256"/>
       <c r="E5" s="236"/>
     </row>
     <row r="6" spans="1:5" ht="13.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="152" t="s">
         <v>192</v>
       </c>
-      <c r="B6" s="276" t="s">
+      <c r="B6" s="254" t="s">
         <v>268</v>
       </c>
-      <c r="C6" s="276"/>
-      <c r="D6" s="276"/>
+      <c r="C6" s="254"/>
+      <c r="D6" s="254"/>
       <c r="E6" s="173"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
@@ -6034,42 +6025,42 @@
       <c r="A9" s="218" t="s">
         <v>186</v>
       </c>
-      <c r="B9" s="268" t="s">
+      <c r="B9" s="256" t="s">
         <v>191</v>
       </c>
-      <c r="C9" s="268"/>
-      <c r="D9" s="268"/>
+      <c r="C9" s="256"/>
+      <c r="D9" s="256"/>
       <c r="E9" s="173"/>
     </row>
     <row r="10" spans="1:5" ht="69" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="218" t="s">
         <v>188</v>
       </c>
-      <c r="B10" s="268" t="s">
+      <c r="B10" s="256" t="s">
         <v>266</v>
       </c>
-      <c r="C10" s="268"/>
-      <c r="D10" s="268"/>
+      <c r="C10" s="256"/>
+      <c r="D10" s="256"/>
       <c r="E10" s="173"/>
     </row>
     <row r="11" spans="1:5" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="269" t="s">
+      <c r="A11" s="274" t="s">
         <v>192</v>
       </c>
-      <c r="B11" s="268" t="s">
+      <c r="B11" s="256" t="s">
         <v>255</v>
       </c>
-      <c r="C11" s="268"/>
-      <c r="D11" s="268"/>
+      <c r="C11" s="256"/>
+      <c r="D11" s="256"/>
       <c r="E11" s="173"/>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A12" s="269"/>
-      <c r="B12" s="278" t="s">
+      <c r="A12" s="274"/>
+      <c r="B12" s="258" t="s">
         <v>193</v>
       </c>
-      <c r="C12" s="278"/>
-      <c r="D12" s="278"/>
+      <c r="C12" s="258"/>
+      <c r="D12" s="258"/>
       <c r="E12" s="223"/>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
@@ -6094,31 +6085,31 @@
       <c r="A16" s="152" t="s">
         <v>186</v>
       </c>
-      <c r="B16" s="268" t="s">
+      <c r="B16" s="256" t="s">
         <v>256</v>
       </c>
-      <c r="C16" s="268"/>
-      <c r="D16" s="268"/>
+      <c r="C16" s="256"/>
+      <c r="D16" s="256"/>
       <c r="E16" s="144"/>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" s="152" t="s">
         <v>188</v>
       </c>
-      <c r="B17" s="268" t="s">
+      <c r="B17" s="256" t="s">
         <v>196</v>
       </c>
-      <c r="C17" s="268"/>
-      <c r="D17" s="268"/>
+      <c r="C17" s="256"/>
+      <c r="D17" s="256"/>
       <c r="E17" s="144"/>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" s="159"/>
-      <c r="B18" s="268" t="s">
+      <c r="B18" s="256" t="s">
         <v>257</v>
       </c>
-      <c r="C18" s="268"/>
-      <c r="D18" s="268"/>
+      <c r="C18" s="256"/>
+      <c r="D18" s="256"/>
       <c r="E18" s="236"/>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.3">
@@ -6132,45 +6123,45 @@
     </row>
     <row r="20" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="159"/>
-      <c r="B20" s="277" t="s">
+      <c r="B20" s="257" t="s">
         <v>295</v>
       </c>
-      <c r="C20" s="277"/>
-      <c r="D20" s="277"/>
+      <c r="C20" s="257"/>
+      <c r="D20" s="257"/>
       <c r="E20" s="236"/>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" s="159"/>
-      <c r="B21" s="277"/>
-      <c r="C21" s="277"/>
-      <c r="D21" s="277"/>
+      <c r="B21" s="257"/>
+      <c r="C21" s="257"/>
+      <c r="D21" s="257"/>
       <c r="E21" s="236"/>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22" s="159"/>
-      <c r="B22" s="277"/>
-      <c r="C22" s="277"/>
-      <c r="D22" s="277"/>
+      <c r="B22" s="257"/>
+      <c r="C22" s="257"/>
+      <c r="D22" s="257"/>
       <c r="E22" s="236"/>
     </row>
     <row r="23" spans="1:5" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="160"/>
-      <c r="B23" s="268" t="s">
+      <c r="B23" s="256" t="s">
         <v>258</v>
       </c>
-      <c r="C23" s="268"/>
-      <c r="D23" s="268"/>
+      <c r="C23" s="256"/>
+      <c r="D23" s="256"/>
       <c r="E23" s="173"/>
     </row>
     <row r="24" spans="1:5" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="152" t="s">
         <v>192</v>
       </c>
-      <c r="B24" s="268" t="s">
+      <c r="B24" s="256" t="s">
         <v>267</v>
       </c>
-      <c r="C24" s="268"/>
-      <c r="D24" s="268"/>
+      <c r="C24" s="256"/>
+      <c r="D24" s="256"/>
       <c r="E24" s="144"/>
     </row>
     <row r="26" spans="1:5" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
@@ -6207,28 +6198,28 @@
       <c r="B29" s="164" t="s">
         <v>269</v>
       </c>
-      <c r="C29" s="279" t="s">
+      <c r="C29" s="259" t="s">
         <v>283</v>
       </c>
-      <c r="D29" s="280"/>
+      <c r="D29" s="260"/>
     </row>
     <row r="30" spans="1:5" ht="14.5" x14ac:dyDescent="0.3">
       <c r="B30" s="164" t="s">
         <v>270</v>
       </c>
-      <c r="C30" s="274" t="s">
+      <c r="C30" s="279" t="s">
         <v>204</v>
       </c>
-      <c r="D30" s="275"/>
+      <c r="D30" s="280"/>
     </row>
     <row r="31" spans="1:5" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B31" s="164" t="s">
         <v>271</v>
       </c>
-      <c r="C31" s="270" t="s">
+      <c r="C31" s="275" t="s">
         <v>275</v>
       </c>
-      <c r="D31" s="272" t="s">
+      <c r="D31" s="277" t="s">
         <v>275</v>
       </c>
     </row>
@@ -6236,31 +6227,31 @@
       <c r="B32" s="164" t="s">
         <v>272</v>
       </c>
-      <c r="C32" s="271"/>
-      <c r="D32" s="273"/>
+      <c r="C32" s="276"/>
+      <c r="D32" s="278"/>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B33" s="164" t="s">
         <v>273</v>
       </c>
-      <c r="C33" s="271"/>
-      <c r="D33" s="273"/>
+      <c r="C33" s="276"/>
+      <c r="D33" s="278"/>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B34" s="164" t="s">
         <v>277</v>
       </c>
-      <c r="C34" s="271"/>
-      <c r="D34" s="273"/>
+      <c r="C34" s="276"/>
+      <c r="D34" s="278"/>
     </row>
     <row r="35" spans="1:5" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B35" s="164" t="s">
         <v>278</v>
       </c>
-      <c r="C35" s="261" t="s">
+      <c r="C35" s="268" t="s">
         <v>276</v>
       </c>
-      <c r="D35" s="264" t="s">
+      <c r="D35" s="271" t="s">
         <v>276</v>
       </c>
     </row>
@@ -6268,23 +6259,23 @@
       <c r="B36" s="164" t="s">
         <v>279</v>
       </c>
-      <c r="C36" s="262"/>
-      <c r="D36" s="265"/>
+      <c r="C36" s="269"/>
+      <c r="D36" s="272"/>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B37" s="164" t="s">
         <v>205</v>
       </c>
-      <c r="C37" s="262"/>
-      <c r="D37" s="265"/>
+      <c r="C37" s="269"/>
+      <c r="D37" s="272"/>
     </row>
     <row r="38" spans="1:5" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A38" s="165"/>
       <c r="B38" s="166" t="s">
         <v>254</v>
       </c>
-      <c r="C38" s="263"/>
-      <c r="D38" s="266"/>
+      <c r="C38" s="270"/>
+      <c r="D38" s="273"/>
     </row>
     <row r="39" spans="1:5" s="167" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B39" s="247" t="s">
@@ -6296,77 +6287,77 @@
     </row>
     <row r="40" spans="1:5" s="167" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A40" s="169"/>
-      <c r="B40" s="267" t="s">
+      <c r="B40" s="255" t="s">
         <v>274</v>
       </c>
-      <c r="C40" s="267"/>
-      <c r="D40" s="267"/>
+      <c r="C40" s="255"/>
+      <c r="D40" s="255"/>
       <c r="E40" s="237"/>
     </row>
     <row r="41" spans="1:5" s="167" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="169"/>
-      <c r="B41" s="267" t="s">
+      <c r="B41" s="255" t="s">
         <v>293</v>
       </c>
-      <c r="C41" s="267"/>
-      <c r="D41" s="267"/>
+      <c r="C41" s="255"/>
+      <c r="D41" s="255"/>
       <c r="E41" s="237"/>
     </row>
     <row r="42" spans="1:5" s="167" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="169"/>
-      <c r="B42" s="267" t="s">
+      <c r="B42" s="255" t="s">
         <v>289</v>
       </c>
-      <c r="C42" s="267"/>
-      <c r="D42" s="267"/>
+      <c r="C42" s="255"/>
+      <c r="D42" s="255"/>
       <c r="E42" s="238"/>
     </row>
     <row r="43" spans="1:5" s="167" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="169"/>
-      <c r="B43" s="267"/>
-      <c r="C43" s="267"/>
-      <c r="D43" s="267"/>
+      <c r="B43" s="255"/>
+      <c r="C43" s="255"/>
+      <c r="D43" s="255"/>
       <c r="E43" s="238"/>
     </row>
     <row r="44" spans="1:5" s="167" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A44" s="169"/>
-      <c r="B44" s="267" t="s">
+      <c r="B44" s="255" t="s">
         <v>294</v>
       </c>
-      <c r="C44" s="267"/>
-      <c r="D44" s="267"/>
+      <c r="C44" s="255"/>
+      <c r="D44" s="255"/>
       <c r="E44" s="237"/>
     </row>
     <row r="45" spans="1:5" s="167" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="169"/>
-      <c r="B45" s="267" t="s">
+      <c r="B45" s="255" t="s">
         <v>288</v>
       </c>
-      <c r="C45" s="267"/>
-      <c r="D45" s="267"/>
+      <c r="C45" s="255"/>
+      <c r="D45" s="255"/>
       <c r="E45" s="237"/>
     </row>
     <row r="46" spans="1:5" s="167" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="169"/>
-      <c r="B46" s="267"/>
-      <c r="C46" s="267"/>
-      <c r="D46" s="267"/>
+      <c r="B46" s="255"/>
+      <c r="C46" s="255"/>
+      <c r="D46" s="255"/>
       <c r="E46" s="237"/>
     </row>
     <row r="47" spans="1:5" s="167" customFormat="1" ht="11.5" x14ac:dyDescent="0.25">
       <c r="A47" s="169"/>
-      <c r="B47" s="267"/>
-      <c r="C47" s="267"/>
-      <c r="D47" s="267"/>
+      <c r="B47" s="255"/>
+      <c r="C47" s="255"/>
+      <c r="D47" s="255"/>
       <c r="E47" s="170"/>
     </row>
     <row r="48" spans="1:5" s="167" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A48" s="169"/>
-      <c r="B48" s="267" t="s">
+      <c r="B48" s="255" t="s">
         <v>290</v>
       </c>
-      <c r="C48" s="267"/>
-      <c r="D48" s="267"/>
+      <c r="C48" s="255"/>
+      <c r="D48" s="255"/>
       <c r="E48" s="170"/>
     </row>
     <row r="49" spans="1:5" s="167" customFormat="1" x14ac:dyDescent="0.25">
@@ -6412,49 +6403,35 @@
       <c r="B53" s="235" t="s">
         <v>209</v>
       </c>
-      <c r="C53" s="259" t="s">
+      <c r="C53" s="266" t="s">
         <v>210</v>
       </c>
-      <c r="D53" s="260"/>
+      <c r="D53" s="267"/>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A54" s="175"/>
       <c r="B54" s="234" t="s">
         <v>280</v>
       </c>
-      <c r="C54" s="254" t="s">
+      <c r="C54" s="261" t="s">
         <v>204</v>
       </c>
-      <c r="D54" s="255"/>
+      <c r="D54" s="262"/>
     </row>
     <row r="55" spans="1:5" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B55" s="239" t="s">
         <v>281</v>
       </c>
-      <c r="C55" s="256" t="s">
+      <c r="C55" s="263" t="s">
         <v>282</v>
       </c>
-      <c r="D55" s="257"/>
+      <c r="D55" s="264"/>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B59" s="175"/>
     </row>
   </sheetData>
   <mergeCells count="30">
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="B45:D47"/>
-    <mergeCell ref="B18:D18"/>
-    <mergeCell ref="B23:D23"/>
-    <mergeCell ref="B48:D48"/>
-    <mergeCell ref="B20:D22"/>
-    <mergeCell ref="B9:D9"/>
-    <mergeCell ref="B10:D10"/>
-    <mergeCell ref="B12:D12"/>
-    <mergeCell ref="B16:D16"/>
-    <mergeCell ref="B17:D17"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="B42:D43"/>
-    <mergeCell ref="B44:D44"/>
     <mergeCell ref="C54:D54"/>
     <mergeCell ref="C55:D55"/>
     <mergeCell ref="A1:D1"/>
@@ -6471,6 +6448,20 @@
     <mergeCell ref="C30:D30"/>
     <mergeCell ref="B4:D4"/>
     <mergeCell ref="B5:D5"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="B45:D47"/>
+    <mergeCell ref="B18:D18"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="B48:D48"/>
+    <mergeCell ref="B20:D22"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="B10:D10"/>
+    <mergeCell ref="B12:D12"/>
+    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="B42:D43"/>
+    <mergeCell ref="B44:D44"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="B12" r:id="rId1" xr:uid="{00000000-0004-0000-0200-000000000000}"/>
@@ -6837,10 +6828,10 @@
     </row>
     <row r="14" spans="1:25" ht="22.5" x14ac:dyDescent="0.45">
       <c r="A14" s="85"/>
-      <c r="B14" s="282" t="s">
+      <c r="B14" s="289" t="s">
         <v>22</v>
       </c>
-      <c r="C14" s="283"/>
+      <c r="C14" s="290"/>
       <c r="D14" s="88" t="s">
         <v>262</v>
       </c>
@@ -6861,10 +6852,10 @@
     </row>
     <row r="15" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A15" s="85"/>
-      <c r="B15" s="284" t="s">
+      <c r="B15" s="291" t="s">
         <v>36</v>
       </c>
-      <c r="C15" s="285"/>
+      <c r="C15" s="292"/>
       <c r="D15" s="120" t="s">
         <v>161</v>
       </c>
@@ -6914,11 +6905,11 @@
       <c r="D17" s="88" t="s">
         <v>15</v>
       </c>
-      <c r="E17" s="286" t="s">
+      <c r="E17" s="293" t="s">
         <v>69</v>
       </c>
-      <c r="F17" s="286"/>
-      <c r="G17" s="286"/>
+      <c r="F17" s="293"/>
+      <c r="G17" s="293"/>
       <c r="H17" s="88" t="s">
         <v>287</v>
       </c>
@@ -6934,11 +6925,11 @@
       <c r="B18" s="133"/>
       <c r="C18" s="133"/>
       <c r="D18" s="134"/>
-      <c r="E18" s="287" t="s">
+      <c r="E18" s="294" t="s">
         <v>169</v>
       </c>
-      <c r="F18" s="287"/>
-      <c r="G18" s="287"/>
+      <c r="F18" s="294"/>
+      <c r="G18" s="294"/>
       <c r="H18" s="134"/>
       <c r="I18" s="82"/>
       <c r="Q18" s="79"/>
@@ -6958,11 +6949,11 @@
       <c r="D19" s="93">
         <v>5</v>
       </c>
-      <c r="E19" s="281" t="s">
+      <c r="E19" s="288" t="s">
         <v>71</v>
       </c>
-      <c r="F19" s="281"/>
-      <c r="G19" s="281"/>
+      <c r="F19" s="288"/>
+      <c r="G19" s="288"/>
       <c r="H19" s="242"/>
       <c r="I19" s="83"/>
       <c r="N19" s="83"/>
@@ -6985,11 +6976,11 @@
       <c r="D20" s="93">
         <v>2</v>
       </c>
-      <c r="E20" s="281" t="s">
+      <c r="E20" s="288" t="s">
         <v>10</v>
       </c>
-      <c r="F20" s="281"/>
-      <c r="G20" s="281"/>
+      <c r="F20" s="288"/>
+      <c r="G20" s="288"/>
       <c r="H20" s="242"/>
       <c r="I20" s="83"/>
       <c r="N20" s="83"/>
@@ -7012,11 +7003,11 @@
       <c r="D21" s="93">
         <v>3</v>
       </c>
-      <c r="E21" s="281" t="s">
+      <c r="E21" s="288" t="s">
         <v>168</v>
       </c>
-      <c r="F21" s="281"/>
-      <c r="G21" s="281"/>
+      <c r="F21" s="288"/>
+      <c r="G21" s="288"/>
       <c r="H21" s="242"/>
       <c r="I21" s="83"/>
       <c r="N21" s="83"/>
@@ -7036,9 +7027,9 @@
         <f>Night</f>
         <v/>
       </c>
-      <c r="E22" s="281"/>
-      <c r="F22" s="281"/>
-      <c r="G22" s="281"/>
+      <c r="E22" s="288"/>
+      <c r="F22" s="288"/>
+      <c r="G22" s="288"/>
       <c r="H22" s="242"/>
       <c r="I22" s="83"/>
       <c r="N22" s="83"/>
@@ -7058,9 +7049,9 @@
         <f>Night</f>
         <v/>
       </c>
-      <c r="E23" s="281"/>
-      <c r="F23" s="281"/>
-      <c r="G23" s="281"/>
+      <c r="E23" s="288"/>
+      <c r="F23" s="288"/>
+      <c r="G23" s="288"/>
       <c r="H23" s="242"/>
       <c r="I23" s="83"/>
       <c r="K23" s="96"/>
@@ -7235,41 +7226,41 @@
       <c r="Y30" s="97"/>
     </row>
     <row r="31" spans="1:25" ht="58.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="288" t="s">
+      <c r="A31" s="285" t="s">
         <v>1</v>
       </c>
-      <c r="B31" s="289" t="s">
+      <c r="B31" s="282" t="s">
         <v>182</v>
       </c>
-      <c r="C31" s="290" t="s">
+      <c r="C31" s="286" t="s">
         <v>265</v>
       </c>
-      <c r="D31" s="291"/>
-      <c r="E31" s="289" t="s">
+      <c r="D31" s="287"/>
+      <c r="E31" s="282" t="s">
         <v>165</v>
       </c>
-      <c r="F31" s="289" t="s">
+      <c r="F31" s="282" t="s">
         <v>69</v>
       </c>
-      <c r="G31" s="289" t="s">
+      <c r="G31" s="282" t="s">
         <v>21</v>
       </c>
-      <c r="H31" s="293" t="s">
+      <c r="H31" s="283" t="s">
         <v>92</v>
       </c>
-      <c r="I31" s="293" t="s">
+      <c r="I31" s="283" t="s">
         <v>72</v>
       </c>
-      <c r="J31" s="289" t="s">
+      <c r="J31" s="282" t="s">
         <v>2</v>
       </c>
-      <c r="K31" s="294" t="s">
+      <c r="K31" s="284" t="s">
         <v>263</v>
       </c>
-      <c r="L31" s="292" t="s">
+      <c r="L31" s="281" t="s">
         <v>67</v>
       </c>
-      <c r="M31" s="292" t="s">
+      <c r="M31" s="281" t="s">
         <v>177</v>
       </c>
       <c r="N31" s="99"/>
@@ -7286,23 +7277,23 @@
       <c r="Y31" s="97"/>
     </row>
     <row r="32" spans="1:25" ht="31" x14ac:dyDescent="0.3">
-      <c r="A32" s="288"/>
-      <c r="B32" s="289"/>
+      <c r="A32" s="285"/>
+      <c r="B32" s="282"/>
       <c r="C32" s="101" t="s">
         <v>146</v>
       </c>
       <c r="D32" s="101" t="s">
         <v>147</v>
       </c>
-      <c r="E32" s="289"/>
-      <c r="F32" s="289"/>
-      <c r="G32" s="289"/>
-      <c r="H32" s="293"/>
-      <c r="I32" s="293"/>
-      <c r="J32" s="289"/>
-      <c r="K32" s="294"/>
-      <c r="L32" s="292"/>
-      <c r="M32" s="292"/>
+      <c r="E32" s="282"/>
+      <c r="F32" s="282"/>
+      <c r="G32" s="282"/>
+      <c r="H32" s="283"/>
+      <c r="I32" s="283"/>
+      <c r="J32" s="282"/>
+      <c r="K32" s="284"/>
+      <c r="L32" s="281"/>
+      <c r="M32" s="281"/>
     </row>
     <row r="33" spans="1:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="102">
@@ -7991,18 +7982,6 @@
     <protectedRange sqref="C33:E42" name="Range1"/>
   </protectedRanges>
   <mergeCells count="21">
-    <mergeCell ref="L31:L32"/>
-    <mergeCell ref="M31:M32"/>
-    <mergeCell ref="G31:G32"/>
-    <mergeCell ref="H31:H32"/>
-    <mergeCell ref="I31:I32"/>
-    <mergeCell ref="J31:J32"/>
-    <mergeCell ref="K31:K32"/>
-    <mergeCell ref="A31:A32"/>
-    <mergeCell ref="B31:B32"/>
-    <mergeCell ref="C31:D31"/>
-    <mergeCell ref="E31:E32"/>
-    <mergeCell ref="F31:F32"/>
     <mergeCell ref="E21:G21"/>
     <mergeCell ref="E22:G22"/>
     <mergeCell ref="E23:G23"/>
@@ -8012,25 +7991,37 @@
     <mergeCell ref="E18:G18"/>
     <mergeCell ref="E19:G19"/>
     <mergeCell ref="E20:G20"/>
+    <mergeCell ref="A31:A32"/>
+    <mergeCell ref="B31:B32"/>
+    <mergeCell ref="C31:D31"/>
+    <mergeCell ref="E31:E32"/>
+    <mergeCell ref="F31:F32"/>
+    <mergeCell ref="L31:L32"/>
+    <mergeCell ref="M31:M32"/>
+    <mergeCell ref="G31:G32"/>
+    <mergeCell ref="H31:H32"/>
+    <mergeCell ref="I31:I32"/>
+    <mergeCell ref="J31:J32"/>
+    <mergeCell ref="K31:K32"/>
   </mergeCells>
   <conditionalFormatting sqref="C33:D42">
-    <cfRule type="expression" dxfId="16" priority="1">
+    <cfRule type="expression" dxfId="14" priority="1">
       <formula>$C33&gt;$D33</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L33:M52 K33:K53">
-    <cfRule type="expression" dxfId="15" priority="5">
+    <cfRule type="expression" dxfId="13" priority="5">
       <formula>$D33="L0"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="14" priority="6">
+    <cfRule type="expression" dxfId="12" priority="6">
       <formula>OR($B33&lt;INDIRECT("R"&amp;MATCH($D33,$A:$A,0)&amp;"C2",FALSE),$C33&gt;INDIRECT("R"&amp;MATCH($D33,$A:$A,0)&amp;"C3",FALSE))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="13" priority="7">
+    <cfRule type="expression" dxfId="11" priority="7">
       <formula>OR($C33&lt;INDIRECT("R"&amp;MATCH($D33,$A:$A,0)&amp;"C2",FALSE),$B33&gt;INDIRECT("R"&amp;MATCH($D33,$A:$A,0)&amp;"C3",FALSE))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Z53">
-    <cfRule type="cellIs" dxfId="12" priority="8" operator="notEqual">
+    <cfRule type="cellIs" dxfId="10" priority="8" operator="notEqual">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8417,10 +8408,10 @@
     </row>
     <row r="14" spans="1:25" ht="22.5" x14ac:dyDescent="0.45">
       <c r="A14" s="85"/>
-      <c r="B14" s="282" t="s">
+      <c r="B14" s="289" t="s">
         <v>22</v>
       </c>
-      <c r="C14" s="283"/>
+      <c r="C14" s="290"/>
       <c r="D14" s="88" t="s">
         <v>262</v>
       </c>
@@ -8494,11 +8485,11 @@
       <c r="D17" s="88" t="s">
         <v>15</v>
       </c>
-      <c r="E17" s="286" t="s">
+      <c r="E17" s="293" t="s">
         <v>69</v>
       </c>
-      <c r="F17" s="286"/>
-      <c r="G17" s="286"/>
+      <c r="F17" s="293"/>
+      <c r="G17" s="293"/>
       <c r="H17" s="88" t="s">
         <v>287</v>
       </c>
@@ -8514,11 +8505,11 @@
       <c r="B18" s="133"/>
       <c r="C18" s="133"/>
       <c r="D18" s="134"/>
-      <c r="E18" s="287" t="s">
+      <c r="E18" s="294" t="s">
         <v>8</v>
       </c>
-      <c r="F18" s="287"/>
-      <c r="G18" s="287"/>
+      <c r="F18" s="294"/>
+      <c r="G18" s="294"/>
       <c r="H18" s="134"/>
       <c r="I18" s="82"/>
       <c r="Q18" s="79"/>
@@ -8538,11 +8529,11 @@
       <c r="D19" s="134">
         <v>6</v>
       </c>
-      <c r="E19" s="281" t="s">
-        <v>308</v>
-      </c>
-      <c r="F19" s="281"/>
-      <c r="G19" s="281"/>
+      <c r="E19" s="288" t="s">
+        <v>307</v>
+      </c>
+      <c r="F19" s="288"/>
+      <c r="G19" s="288"/>
       <c r="H19" s="242">
         <v>2</v>
       </c>
@@ -8561,9 +8552,9 @@
       <c r="B20" s="243"/>
       <c r="C20" s="243"/>
       <c r="D20" s="134"/>
-      <c r="E20" s="281"/>
-      <c r="F20" s="281"/>
-      <c r="G20" s="281"/>
+      <c r="E20" s="288"/>
+      <c r="F20" s="288"/>
+      <c r="G20" s="288"/>
       <c r="H20" s="242"/>
       <c r="I20" s="83"/>
       <c r="N20" s="83"/>
@@ -8583,9 +8574,9 @@
         <f>Night</f>
         <v/>
       </c>
-      <c r="E21" s="281"/>
-      <c r="F21" s="281"/>
-      <c r="G21" s="281"/>
+      <c r="E21" s="288"/>
+      <c r="F21" s="288"/>
+      <c r="G21" s="288"/>
       <c r="H21" s="242"/>
       <c r="I21" s="83"/>
       <c r="N21" s="83"/>
@@ -8605,9 +8596,9 @@
         <f>Night</f>
         <v/>
       </c>
-      <c r="E22" s="281"/>
-      <c r="F22" s="281"/>
-      <c r="G22" s="281"/>
+      <c r="E22" s="288"/>
+      <c r="F22" s="288"/>
+      <c r="G22" s="288"/>
       <c r="H22" s="242"/>
       <c r="I22" s="83"/>
       <c r="N22" s="83"/>
@@ -8627,9 +8618,9 @@
         <f>Night</f>
         <v/>
       </c>
-      <c r="E23" s="281"/>
-      <c r="F23" s="281"/>
-      <c r="G23" s="281"/>
+      <c r="E23" s="288"/>
+      <c r="F23" s="288"/>
+      <c r="G23" s="288"/>
       <c r="H23" s="242"/>
       <c r="I23" s="148"/>
       <c r="J23" s="148"/>
@@ -8776,41 +8767,41 @@
       <c r="Y29" s="97"/>
     </row>
     <row r="30" spans="1:25" ht="51.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="288" t="s">
+      <c r="A30" s="285" t="s">
         <v>1</v>
       </c>
-      <c r="B30" s="289" t="s">
+      <c r="B30" s="282" t="s">
         <v>182</v>
       </c>
-      <c r="C30" s="290" t="s">
+      <c r="C30" s="286" t="s">
         <v>265</v>
       </c>
-      <c r="D30" s="291"/>
-      <c r="E30" s="289" t="s">
+      <c r="D30" s="287"/>
+      <c r="E30" s="282" t="s">
         <v>165</v>
       </c>
-      <c r="F30" s="289" t="s">
+      <c r="F30" s="282" t="s">
         <v>69</v>
       </c>
-      <c r="G30" s="289" t="s">
+      <c r="G30" s="282" t="s">
         <v>21</v>
       </c>
-      <c r="H30" s="293" t="s">
+      <c r="H30" s="283" t="s">
         <v>92</v>
       </c>
-      <c r="I30" s="293" t="s">
+      <c r="I30" s="283" t="s">
         <v>72</v>
       </c>
-      <c r="J30" s="289" t="s">
+      <c r="J30" s="282" t="s">
         <v>2</v>
       </c>
-      <c r="K30" s="294" t="s">
+      <c r="K30" s="284" t="s">
         <v>263</v>
       </c>
-      <c r="L30" s="292" t="s">
+      <c r="L30" s="281" t="s">
         <v>67</v>
       </c>
-      <c r="M30" s="292" t="s">
+      <c r="M30" s="281" t="s">
         <v>177</v>
       </c>
       <c r="N30" s="99"/>
@@ -8827,23 +8818,23 @@
       <c r="Y30" s="97"/>
     </row>
     <row r="31" spans="1:25" ht="31" x14ac:dyDescent="0.3">
-      <c r="A31" s="288"/>
-      <c r="B31" s="289"/>
+      <c r="A31" s="285"/>
+      <c r="B31" s="282"/>
       <c r="C31" s="101" t="s">
         <v>146</v>
       </c>
       <c r="D31" s="101" t="s">
         <v>147</v>
       </c>
-      <c r="E31" s="289"/>
-      <c r="F31" s="289"/>
-      <c r="G31" s="289"/>
-      <c r="H31" s="293"/>
-      <c r="I31" s="293"/>
-      <c r="J31" s="289"/>
-      <c r="K31" s="294"/>
-      <c r="L31" s="292"/>
-      <c r="M31" s="292"/>
+      <c r="E31" s="282"/>
+      <c r="F31" s="282"/>
+      <c r="G31" s="282"/>
+      <c r="H31" s="283"/>
+      <c r="I31" s="283"/>
+      <c r="J31" s="282"/>
+      <c r="K31" s="284"/>
+      <c r="L31" s="281"/>
+      <c r="M31" s="281"/>
     </row>
     <row r="32" spans="1:25" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="102">
@@ -8953,7 +8944,7 @@
         <v>56</v>
       </c>
       <c r="H34" s="109" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="I34" s="110">
         <v>600</v>
@@ -9143,7 +9134,7 @@
         <v>58</v>
       </c>
       <c r="H39" s="136" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="I39" s="110">
         <v>35.94</v>
@@ -9181,7 +9172,7 @@
         <v>58</v>
       </c>
       <c r="H40" s="136" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="I40" s="110">
         <v>31.96</v>
@@ -9546,14 +9537,6 @@
     <protectedRange sqref="C41:D41" name="Range1_1"/>
   </protectedRanges>
   <mergeCells count="21">
-    <mergeCell ref="L30:L31"/>
-    <mergeCell ref="M30:M31"/>
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="G30:G31"/>
-    <mergeCell ref="H30:H31"/>
-    <mergeCell ref="I30:I31"/>
-    <mergeCell ref="J30:J31"/>
-    <mergeCell ref="K30:K31"/>
     <mergeCell ref="A30:A31"/>
     <mergeCell ref="B30:B31"/>
     <mergeCell ref="E30:E31"/>
@@ -9567,33 +9550,41 @@
     <mergeCell ref="E21:G21"/>
     <mergeCell ref="E22:G22"/>
     <mergeCell ref="E18:G18"/>
+    <mergeCell ref="L30:L31"/>
+    <mergeCell ref="M30:M31"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="G30:G31"/>
+    <mergeCell ref="H30:H31"/>
+    <mergeCell ref="I30:I31"/>
+    <mergeCell ref="J30:J31"/>
+    <mergeCell ref="K30:K31"/>
   </mergeCells>
   <conditionalFormatting sqref="C32:D52">
-    <cfRule type="expression" dxfId="11" priority="1">
+    <cfRule type="expression" dxfId="9" priority="1">
       <formula>$C32&gt;$D32</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K52:L52 K32:K41">
-    <cfRule type="expression" dxfId="10" priority="12">
+  <conditionalFormatting sqref="K32:K41 K52:L52">
+    <cfRule type="expression" dxfId="8" priority="12">
       <formula>$D32="L0"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="9" priority="14">
+    <cfRule type="expression" dxfId="7" priority="14">
       <formula>OR($B32&lt;INDIRECT("R"&amp;MATCH($D32,$A:$A,0)&amp;"C2",FALSE),$C32&gt;INDIRECT("R"&amp;MATCH($D32,$A:$A,0)&amp;"C3",FALSE))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="8" priority="15">
+    <cfRule type="expression" dxfId="6" priority="15">
       <formula>OR($C32&lt;INDIRECT("R"&amp;MATCH($D32,$A:$A,0)&amp;"C2",FALSE),$B32&gt;INDIRECT("R"&amp;MATCH($D32,$A:$A,0)&amp;"C3",FALSE))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L32:M51">
-    <cfRule type="expression" dxfId="7" priority="23">
+    <cfRule type="expression" dxfId="5" priority="23">
       <formula>$E32="L0"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="6" priority="25">
+    <cfRule type="expression" dxfId="4" priority="25">
       <formula>IF($C32="", OR( $B32&lt;INDIRECT("R"&amp;MATCH($E32,$A:$A,0)&amp;"C2",FALSE), $B32&gt;INDIRECT("R"&amp;MATCH($E32,$A:$A,0)&amp;"C3",FALSE)), OR( $C32&lt;INDIRECT("R"&amp;MATCH($E32,$A:$A,0)&amp;"C2",FALSE), $D32&gt;INDIRECT("R"&amp;MATCH($E32,$A:$A,0)&amp;"C3",FALSE)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Z52">
-    <cfRule type="cellIs" dxfId="5" priority="19" operator="notEqual">
+    <cfRule type="cellIs" dxfId="3" priority="19" operator="notEqual">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9661,27 +9652,27 @@
   <sheetData>
     <row r="2" spans="1:20" ht="52.5" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="1:20" ht="25" x14ac:dyDescent="0.5">
-      <c r="A3" s="304" t="s">
+      <c r="A3" s="299" t="s">
         <v>264</v>
       </c>
-      <c r="B3" s="304"/>
-      <c r="C3" s="304"/>
-      <c r="D3" s="304"/>
-      <c r="E3" s="304"/>
-      <c r="F3" s="304"/>
-      <c r="G3" s="304"/>
-      <c r="H3" s="304"/>
-      <c r="I3" s="304"/>
-      <c r="J3" s="304"/>
-      <c r="K3" s="304"/>
-      <c r="L3" s="304"/>
-      <c r="M3" s="304"/>
-      <c r="N3" s="304"/>
-      <c r="O3" s="304"/>
-      <c r="P3" s="304"/>
-      <c r="Q3" s="304"/>
-      <c r="R3" s="304"/>
-      <c r="S3" s="304"/>
+      <c r="B3" s="299"/>
+      <c r="C3" s="299"/>
+      <c r="D3" s="299"/>
+      <c r="E3" s="299"/>
+      <c r="F3" s="299"/>
+      <c r="G3" s="299"/>
+      <c r="H3" s="299"/>
+      <c r="I3" s="299"/>
+      <c r="J3" s="299"/>
+      <c r="K3" s="299"/>
+      <c r="L3" s="299"/>
+      <c r="M3" s="299"/>
+      <c r="N3" s="299"/>
+      <c r="O3" s="299"/>
+      <c r="P3" s="299"/>
+      <c r="Q3" s="299"/>
+      <c r="R3" s="299"/>
+      <c r="S3" s="299"/>
     </row>
     <row r="4" spans="1:20" ht="3.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="5" spans="1:20" ht="20.5" thickBot="1" x14ac:dyDescent="0.45">
@@ -9712,27 +9703,27 @@
       <c r="A6" s="177" t="s">
         <v>211</v>
       </c>
-      <c r="B6" s="305" t="s">
+      <c r="B6" s="300" t="s">
         <v>212</v>
       </c>
-      <c r="C6" s="305"/>
-      <c r="D6" s="305"/>
-      <c r="E6" s="305"/>
-      <c r="F6" s="305"/>
-      <c r="G6" s="305"/>
-      <c r="H6" s="305"/>
-      <c r="I6" s="305"/>
-      <c r="J6" s="305"/>
-      <c r="K6" s="305"/>
-      <c r="L6" s="305"/>
-      <c r="M6" s="305"/>
-      <c r="N6" s="305"/>
-      <c r="O6" s="305"/>
-      <c r="P6" s="305"/>
-      <c r="Q6" s="305"/>
-      <c r="R6" s="305"/>
-      <c r="S6" s="305"/>
-      <c r="T6" s="306"/>
+      <c r="C6" s="300"/>
+      <c r="D6" s="300"/>
+      <c r="E6" s="300"/>
+      <c r="F6" s="300"/>
+      <c r="G6" s="300"/>
+      <c r="H6" s="300"/>
+      <c r="I6" s="300"/>
+      <c r="J6" s="300"/>
+      <c r="K6" s="300"/>
+      <c r="L6" s="300"/>
+      <c r="M6" s="300"/>
+      <c r="N6" s="300"/>
+      <c r="O6" s="300"/>
+      <c r="P6" s="300"/>
+      <c r="Q6" s="300"/>
+      <c r="R6" s="300"/>
+      <c r="S6" s="300"/>
+      <c r="T6" s="301"/>
     </row>
     <row r="7" spans="1:20" ht="3.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="178"/>
@@ -9760,36 +9751,36 @@
       <c r="A8" s="178" t="s">
         <v>213</v>
       </c>
-      <c r="B8" s="303" t="s">
+      <c r="B8" s="298" t="s">
         <v>214</v>
       </c>
-      <c r="C8" s="302"/>
-      <c r="D8" s="302"/>
-      <c r="E8" s="302"/>
-      <c r="F8" s="302"/>
-      <c r="G8" s="302"/>
-      <c r="H8" s="302"/>
-      <c r="I8" s="302"/>
-      <c r="J8" s="302"/>
-      <c r="K8" s="302"/>
-      <c r="L8" s="302"/>
-      <c r="M8" s="302"/>
-      <c r="N8" s="302"/>
-      <c r="O8" s="302"/>
-      <c r="P8" s="302"/>
-      <c r="Q8" s="302"/>
-      <c r="R8" s="302"/>
-      <c r="S8" s="302"/>
+      <c r="C8" s="297"/>
+      <c r="D8" s="297"/>
+      <c r="E8" s="297"/>
+      <c r="F8" s="297"/>
+      <c r="G8" s="297"/>
+      <c r="H8" s="297"/>
+      <c r="I8" s="297"/>
+      <c r="J8" s="297"/>
+      <c r="K8" s="297"/>
+      <c r="L8" s="297"/>
+      <c r="M8" s="297"/>
+      <c r="N8" s="297"/>
+      <c r="O8" s="297"/>
+      <c r="P8" s="297"/>
+      <c r="Q8" s="297"/>
+      <c r="R8" s="297"/>
+      <c r="S8" s="297"/>
       <c r="T8" s="180"/>
     </row>
     <row r="9" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="178"/>
-      <c r="B9" s="302" t="s">
+      <c r="B9" s="297" t="s">
         <v>215</v>
       </c>
-      <c r="C9" s="302"/>
-      <c r="D9" s="302"/>
-      <c r="E9" s="302"/>
+      <c r="C9" s="297"/>
+      <c r="D9" s="297"/>
+      <c r="E9" s="297"/>
       <c r="F9" s="182"/>
       <c r="G9" s="216"/>
       <c r="H9" s="216"/>
@@ -9831,12 +9822,12 @@
     </row>
     <row r="11" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="178"/>
-      <c r="B11" s="302" t="s">
+      <c r="B11" s="297" t="s">
         <v>216</v>
       </c>
-      <c r="C11" s="302"/>
-      <c r="D11" s="302"/>
-      <c r="E11" s="302"/>
+      <c r="C11" s="297"/>
+      <c r="D11" s="297"/>
+      <c r="E11" s="297"/>
       <c r="F11" s="179"/>
       <c r="G11" s="179"/>
       <c r="H11" s="215"/>
@@ -9878,21 +9869,21 @@
     </row>
     <row r="13" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="178"/>
-      <c r="B13" s="303" t="s">
+      <c r="B13" s="298" t="s">
         <v>218</v>
       </c>
-      <c r="C13" s="302"/>
-      <c r="D13" s="302"/>
-      <c r="E13" s="302"/>
-      <c r="F13" s="302"/>
-      <c r="G13" s="302"/>
-      <c r="H13" s="302"/>
-      <c r="I13" s="302"/>
-      <c r="J13" s="302"/>
-      <c r="K13" s="302"/>
-      <c r="L13" s="302"/>
-      <c r="M13" s="302"/>
-      <c r="N13" s="302"/>
+      <c r="C13" s="297"/>
+      <c r="D13" s="297"/>
+      <c r="E13" s="297"/>
+      <c r="F13" s="297"/>
+      <c r="G13" s="297"/>
+      <c r="H13" s="297"/>
+      <c r="I13" s="297"/>
+      <c r="J13" s="297"/>
+      <c r="K13" s="297"/>
+      <c r="L13" s="297"/>
+      <c r="M13" s="297"/>
+      <c r="N13" s="297"/>
       <c r="O13" s="181"/>
       <c r="P13" s="181"/>
       <c r="Q13" s="181"/>
@@ -9902,19 +9893,19 @@
     </row>
     <row r="14" spans="1:20" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="178"/>
-      <c r="B14" s="302"/>
-      <c r="C14" s="302"/>
-      <c r="D14" s="302"/>
-      <c r="E14" s="302"/>
-      <c r="F14" s="302"/>
-      <c r="G14" s="302"/>
-      <c r="H14" s="302"/>
-      <c r="I14" s="302"/>
-      <c r="J14" s="302"/>
-      <c r="K14" s="302"/>
-      <c r="L14" s="302"/>
-      <c r="M14" s="302"/>
-      <c r="N14" s="302"/>
+      <c r="B14" s="297"/>
+      <c r="C14" s="297"/>
+      <c r="D14" s="297"/>
+      <c r="E14" s="297"/>
+      <c r="F14" s="297"/>
+      <c r="G14" s="297"/>
+      <c r="H14" s="297"/>
+      <c r="I14" s="297"/>
+      <c r="J14" s="297"/>
+      <c r="K14" s="297"/>
+      <c r="L14" s="297"/>
+      <c r="M14" s="297"/>
+      <c r="N14" s="297"/>
       <c r="O14" s="179"/>
       <c r="P14" s="179"/>
       <c r="Q14" s="179"/>
@@ -10024,20 +10015,20 @@
         <v>221</v>
       </c>
       <c r="E19" s="190"/>
-      <c r="F19" s="298" t="s">
+      <c r="F19" s="303" t="s">
         <v>222</v>
       </c>
-      <c r="G19" s="298"/>
-      <c r="H19" s="298"/>
-      <c r="I19" s="298"/>
-      <c r="J19" s="298"/>
-      <c r="K19" s="298"/>
-      <c r="L19" s="298"/>
-      <c r="M19" s="298"/>
-      <c r="N19" s="298"/>
-      <c r="O19" s="298"/>
-      <c r="P19" s="298"/>
-      <c r="Q19" s="298"/>
+      <c r="G19" s="303"/>
+      <c r="H19" s="303"/>
+      <c r="I19" s="303"/>
+      <c r="J19" s="303"/>
+      <c r="K19" s="303"/>
+      <c r="L19" s="303"/>
+      <c r="M19" s="303"/>
+      <c r="N19" s="303"/>
+      <c r="O19" s="303"/>
+      <c r="P19" s="303"/>
+      <c r="Q19" s="303"/>
       <c r="R19" s="198"/>
       <c r="S19" s="199" t="str">
         <f>'Reimbursement details'!D15</f>
@@ -10078,20 +10069,20 @@
         <v>SHEN Leming</v>
       </c>
       <c r="E21" s="190"/>
-      <c r="F21" s="298" t="s">
+      <c r="F21" s="303" t="s">
         <v>224</v>
       </c>
-      <c r="G21" s="298"/>
-      <c r="H21" s="298"/>
-      <c r="I21" s="298"/>
-      <c r="J21" s="298"/>
-      <c r="K21" s="298"/>
-      <c r="L21" s="298"/>
-      <c r="M21" s="298"/>
-      <c r="N21" s="298"/>
-      <c r="O21" s="298"/>
-      <c r="P21" s="298"/>
-      <c r="Q21" s="298"/>
+      <c r="G21" s="303"/>
+      <c r="H21" s="303"/>
+      <c r="I21" s="303"/>
+      <c r="J21" s="303"/>
+      <c r="K21" s="303"/>
+      <c r="L21" s="303"/>
+      <c r="M21" s="303"/>
+      <c r="N21" s="303"/>
+      <c r="O21" s="303"/>
+      <c r="P21" s="303"/>
+      <c r="Q21" s="303"/>
       <c r="R21" s="198"/>
       <c r="S21" s="199" t="str">
         <f>'Reimbursement details'!E15</f>
@@ -10133,20 +10124,20 @@
         <v>296</v>
       </c>
       <c r="E23" s="190"/>
-      <c r="F23" s="298" t="s">
+      <c r="F23" s="303" t="s">
         <v>227</v>
       </c>
-      <c r="G23" s="298"/>
-      <c r="H23" s="298"/>
-      <c r="I23" s="298"/>
-      <c r="J23" s="298"/>
-      <c r="K23" s="298"/>
-      <c r="L23" s="298"/>
-      <c r="M23" s="298"/>
-      <c r="N23" s="298"/>
-      <c r="O23" s="298"/>
-      <c r="P23" s="298"/>
-      <c r="Q23" s="298"/>
+      <c r="G23" s="303"/>
+      <c r="H23" s="303"/>
+      <c r="I23" s="303"/>
+      <c r="J23" s="303"/>
+      <c r="K23" s="303"/>
+      <c r="L23" s="303"/>
+      <c r="M23" s="303"/>
+      <c r="N23" s="303"/>
+      <c r="O23" s="303"/>
+      <c r="P23" s="303"/>
+      <c r="Q23" s="303"/>
       <c r="R23" s="198"/>
       <c r="S23" s="225">
         <v>62371304</v>
@@ -10607,9 +10598,9 @@
     <row r="43" spans="1:20" ht="20.5" x14ac:dyDescent="0.45">
       <c r="A43" s="196"/>
       <c r="B43" s="190"/>
-      <c r="C43" s="300"/>
-      <c r="D43" s="300"/>
-      <c r="E43" s="300"/>
+      <c r="C43" s="305"/>
+      <c r="D43" s="305"/>
+      <c r="E43" s="305"/>
       <c r="F43" s="190"/>
       <c r="G43" s="190"/>
       <c r="H43" s="190"/>
@@ -10781,8 +10772,8 @@
       </c>
       <c r="B50" s="121"/>
       <c r="C50" s="190"/>
-      <c r="D50" s="209" t="s">
-        <v>307</v>
+      <c r="D50" s="325" t="s">
+        <v>311</v>
       </c>
       <c r="E50" s="190"/>
       <c r="F50" s="190"/>
@@ -10895,98 +10886,98 @@
     </row>
     <row r="55" spans="1:20" ht="40.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A55" s="229"/>
-      <c r="B55" s="301" t="s">
+      <c r="B55" s="306" t="s">
         <v>251</v>
       </c>
-      <c r="C55" s="301"/>
-      <c r="D55" s="301"/>
-      <c r="E55" s="301"/>
-      <c r="F55" s="301"/>
-      <c r="G55" s="301"/>
-      <c r="H55" s="301"/>
-      <c r="I55" s="301"/>
-      <c r="J55" s="301"/>
-      <c r="K55" s="301"/>
-      <c r="L55" s="301"/>
-      <c r="M55" s="301"/>
-      <c r="N55" s="301"/>
-      <c r="O55" s="301"/>
-      <c r="P55" s="301"/>
-      <c r="Q55" s="301"/>
-      <c r="R55" s="301"/>
-      <c r="S55" s="301"/>
+      <c r="C55" s="306"/>
+      <c r="D55" s="306"/>
+      <c r="E55" s="306"/>
+      <c r="F55" s="306"/>
+      <c r="G55" s="306"/>
+      <c r="H55" s="306"/>
+      <c r="I55" s="306"/>
+      <c r="J55" s="306"/>
+      <c r="K55" s="306"/>
+      <c r="L55" s="306"/>
+      <c r="M55" s="306"/>
+      <c r="N55" s="306"/>
+      <c r="O55" s="306"/>
+      <c r="P55" s="306"/>
+      <c r="Q55" s="306"/>
+      <c r="R55" s="306"/>
+      <c r="S55" s="306"/>
       <c r="T55" s="200"/>
     </row>
     <row r="56" spans="1:20" ht="20.5" x14ac:dyDescent="0.45">
       <c r="A56" s="229"/>
-      <c r="B56" s="297" t="s">
+      <c r="B56" s="302" t="s">
         <v>252</v>
       </c>
-      <c r="C56" s="298"/>
-      <c r="D56" s="298"/>
-      <c r="E56" s="298"/>
-      <c r="F56" s="298"/>
-      <c r="G56" s="298"/>
-      <c r="H56" s="298"/>
-      <c r="I56" s="298"/>
-      <c r="J56" s="298"/>
-      <c r="K56" s="298"/>
-      <c r="L56" s="298"/>
-      <c r="M56" s="298"/>
-      <c r="N56" s="298"/>
-      <c r="O56" s="298"/>
-      <c r="P56" s="298"/>
-      <c r="Q56" s="298"/>
-      <c r="R56" s="298"/>
-      <c r="S56" s="298"/>
+      <c r="C56" s="303"/>
+      <c r="D56" s="303"/>
+      <c r="E56" s="303"/>
+      <c r="F56" s="303"/>
+      <c r="G56" s="303"/>
+      <c r="H56" s="303"/>
+      <c r="I56" s="303"/>
+      <c r="J56" s="303"/>
+      <c r="K56" s="303"/>
+      <c r="L56" s="303"/>
+      <c r="M56" s="303"/>
+      <c r="N56" s="303"/>
+      <c r="O56" s="303"/>
+      <c r="P56" s="303"/>
+      <c r="Q56" s="303"/>
+      <c r="R56" s="303"/>
+      <c r="S56" s="303"/>
       <c r="T56" s="200"/>
     </row>
     <row r="57" spans="1:20" ht="20.5" x14ac:dyDescent="0.45">
       <c r="A57" s="229"/>
-      <c r="B57" s="297" t="s">
+      <c r="B57" s="302" t="s">
         <v>253</v>
       </c>
-      <c r="C57" s="298"/>
-      <c r="D57" s="298"/>
-      <c r="E57" s="298"/>
-      <c r="F57" s="298"/>
-      <c r="G57" s="298"/>
-      <c r="H57" s="298"/>
-      <c r="I57" s="298"/>
-      <c r="J57" s="298"/>
-      <c r="K57" s="298"/>
-      <c r="L57" s="298"/>
-      <c r="M57" s="298"/>
-      <c r="N57" s="298"/>
-      <c r="O57" s="298"/>
-      <c r="P57" s="298"/>
-      <c r="Q57" s="298"/>
-      <c r="R57" s="298"/>
-      <c r="S57" s="298"/>
+      <c r="C57" s="303"/>
+      <c r="D57" s="303"/>
+      <c r="E57" s="303"/>
+      <c r="F57" s="303"/>
+      <c r="G57" s="303"/>
+      <c r="H57" s="303"/>
+      <c r="I57" s="303"/>
+      <c r="J57" s="303"/>
+      <c r="K57" s="303"/>
+      <c r="L57" s="303"/>
+      <c r="M57" s="303"/>
+      <c r="N57" s="303"/>
+      <c r="O57" s="303"/>
+      <c r="P57" s="303"/>
+      <c r="Q57" s="303"/>
+      <c r="R57" s="303"/>
+      <c r="S57" s="303"/>
       <c r="T57" s="200"/>
     </row>
     <row r="58" spans="1:20" ht="20.5" x14ac:dyDescent="0.45">
       <c r="A58" s="229"/>
-      <c r="B58" s="297" t="s">
+      <c r="B58" s="302" t="s">
         <v>260</v>
       </c>
-      <c r="C58" s="298"/>
-      <c r="D58" s="298"/>
-      <c r="E58" s="298"/>
-      <c r="F58" s="298"/>
-      <c r="G58" s="298"/>
-      <c r="H58" s="298"/>
-      <c r="I58" s="298"/>
-      <c r="J58" s="298"/>
-      <c r="K58" s="298"/>
-      <c r="L58" s="298"/>
-      <c r="M58" s="298"/>
-      <c r="N58" s="298"/>
-      <c r="O58" s="298"/>
-      <c r="P58" s="298"/>
-      <c r="Q58" s="298"/>
-      <c r="R58" s="298"/>
-      <c r="S58" s="298"/>
+      <c r="C58" s="303"/>
+      <c r="D58" s="303"/>
+      <c r="E58" s="303"/>
+      <c r="F58" s="303"/>
+      <c r="G58" s="303"/>
+      <c r="H58" s="303"/>
+      <c r="I58" s="303"/>
+      <c r="J58" s="303"/>
+      <c r="K58" s="303"/>
+      <c r="L58" s="303"/>
+      <c r="M58" s="303"/>
+      <c r="N58" s="303"/>
+      <c r="O58" s="303"/>
+      <c r="P58" s="303"/>
+      <c r="Q58" s="303"/>
+      <c r="R58" s="303"/>
+      <c r="S58" s="303"/>
       <c r="T58" s="200"/>
     </row>
     <row r="59" spans="1:20" ht="20.5" x14ac:dyDescent="0.45">
@@ -11015,26 +11006,26 @@
     </row>
     <row r="60" spans="1:20" ht="20.5" x14ac:dyDescent="0.45">
       <c r="A60" s="229"/>
-      <c r="B60" s="297" t="s">
+      <c r="B60" s="302" t="s">
         <v>247</v>
       </c>
-      <c r="C60" s="298"/>
-      <c r="D60" s="298"/>
-      <c r="E60" s="298"/>
-      <c r="F60" s="298"/>
-      <c r="G60" s="298"/>
-      <c r="H60" s="298"/>
-      <c r="I60" s="298"/>
-      <c r="J60" s="298"/>
-      <c r="K60" s="298"/>
-      <c r="L60" s="298"/>
-      <c r="M60" s="298"/>
-      <c r="N60" s="298"/>
-      <c r="O60" s="298"/>
-      <c r="P60" s="298"/>
-      <c r="Q60" s="298"/>
-      <c r="R60" s="298"/>
-      <c r="S60" s="298"/>
+      <c r="C60" s="303"/>
+      <c r="D60" s="303"/>
+      <c r="E60" s="303"/>
+      <c r="F60" s="303"/>
+      <c r="G60" s="303"/>
+      <c r="H60" s="303"/>
+      <c r="I60" s="303"/>
+      <c r="J60" s="303"/>
+      <c r="K60" s="303"/>
+      <c r="L60" s="303"/>
+      <c r="M60" s="303"/>
+      <c r="N60" s="303"/>
+      <c r="O60" s="303"/>
+      <c r="P60" s="303"/>
+      <c r="Q60" s="303"/>
+      <c r="R60" s="303"/>
+      <c r="S60" s="303"/>
       <c r="T60" s="200"/>
     </row>
     <row r="61" spans="1:20" ht="21" thickBot="1" x14ac:dyDescent="0.5">
@@ -11073,12 +11064,12 @@
       <c r="K67" s="228"/>
       <c r="L67" s="228"/>
       <c r="M67" s="228"/>
-      <c r="N67" s="299" t="s">
+      <c r="N67" s="304" t="s">
         <v>249</v>
       </c>
-      <c r="O67" s="299"/>
-      <c r="P67" s="299"/>
-      <c r="Q67" s="299"/>
+      <c r="O67" s="304"/>
+      <c r="P67" s="304"/>
+      <c r="Q67" s="304"/>
       <c r="R67" s="207"/>
       <c r="S67" s="252">
         <v>45838</v>
@@ -11095,12 +11086,6 @@
     </row>
   </sheetData>
   <mergeCells count="16">
-    <mergeCell ref="B11:E11"/>
-    <mergeCell ref="B13:N14"/>
-    <mergeCell ref="A3:S3"/>
-    <mergeCell ref="B6:T6"/>
-    <mergeCell ref="B8:S8"/>
-    <mergeCell ref="B9:E9"/>
     <mergeCell ref="B57:S57"/>
     <mergeCell ref="B58:S58"/>
     <mergeCell ref="B60:S60"/>
@@ -11111,6 +11096,12 @@
     <mergeCell ref="C43:E43"/>
     <mergeCell ref="B55:S55"/>
     <mergeCell ref="B56:S56"/>
+    <mergeCell ref="B11:E11"/>
+    <mergeCell ref="B13:N14"/>
+    <mergeCell ref="A3:S3"/>
+    <mergeCell ref="B6:T6"/>
+    <mergeCell ref="B8:S8"/>
+    <mergeCell ref="B9:E9"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="B10" r:id="rId1" xr:uid="{00000000-0004-0000-0500-000000000000}"/>
@@ -11513,10 +11504,10 @@
         <f>MAX('Reimbursement details'!C19:C24)</f>
         <v>45836</v>
       </c>
-      <c r="H3" s="322" t="s">
+      <c r="H3" s="310" t="s">
         <v>101</v>
       </c>
-      <c r="I3" s="323"/>
+      <c r="I3" s="311"/>
       <c r="J3" s="40">
         <v>800</v>
       </c>
@@ -11539,10 +11530,10 @@
         <f>F3</f>
         <v>45836</v>
       </c>
-      <c r="H4" s="322" t="s">
+      <c r="H4" s="310" t="s">
         <v>103</v>
       </c>
-      <c r="I4" s="323"/>
+      <c r="I4" s="311"/>
       <c r="J4" s="140">
         <f>SUM('Reimbursement details'!D19:D24)+SUM('Reimbursement details'!H19:H23)</f>
         <v>8</v>
@@ -11561,10 +11552,10 @@
       <c r="D5" s="42"/>
       <c r="E5" s="37"/>
       <c r="F5" s="42"/>
-      <c r="H5" s="322" t="s">
+      <c r="H5" s="310" t="s">
         <v>105</v>
       </c>
-      <c r="I5" s="323"/>
+      <c r="I5" s="311"/>
       <c r="J5" s="43">
         <f>J3*J4</f>
         <v>6400</v>
@@ -11574,11 +11565,11 @@
       <c r="A6" s="38" t="s">
         <v>106</v>
       </c>
-      <c r="B6" s="316"/>
-      <c r="C6" s="317"/>
-      <c r="D6" s="317"/>
-      <c r="E6" s="317"/>
-      <c r="F6" s="318"/>
+      <c r="B6" s="313"/>
+      <c r="C6" s="314"/>
+      <c r="D6" s="314"/>
+      <c r="E6" s="314"/>
+      <c r="F6" s="315"/>
       <c r="G6" s="44"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.35">
@@ -11595,11 +11586,11 @@
       </c>
       <c r="B8" s="45"/>
       <c r="C8" s="45"/>
-      <c r="D8" s="310" t="s">
+      <c r="D8" s="316" t="s">
         <v>108</v>
       </c>
-      <c r="E8" s="311"/>
-      <c r="F8" s="312"/>
+      <c r="E8" s="317"/>
+      <c r="F8" s="318"/>
       <c r="G8" s="143"/>
       <c r="H8" s="48" t="s">
         <v>109</v>
@@ -11625,9 +11616,9 @@
         <v>4</v>
       </c>
       <c r="C9" s="50"/>
-      <c r="D9" s="310"/>
-      <c r="E9" s="311"/>
-      <c r="F9" s="312"/>
+      <c r="D9" s="316"/>
+      <c r="E9" s="317"/>
+      <c r="F9" s="318"/>
       <c r="G9" s="51"/>
       <c r="H9" s="52">
         <f>SUMIF('Reimbursement details'!$G$32:$G52,"Air passage",'Reimbursement details'!$L32:$L52)</f>
@@ -11642,7 +11633,7 @@
         <f>IFERROR(J9/$H$22*$J$22,0)</f>
         <v>9782.7099999999991</v>
       </c>
-      <c r="L9" s="319">
+      <c r="L9" s="307">
         <f>SUM(K9:K11)</f>
         <v>10315.039999999999</v>
       </c>
@@ -11655,9 +11646,9 @@
         <v>4</v>
       </c>
       <c r="C10" s="50"/>
-      <c r="D10" s="310"/>
-      <c r="E10" s="311"/>
-      <c r="F10" s="312"/>
+      <c r="D10" s="316"/>
+      <c r="E10" s="317"/>
+      <c r="F10" s="318"/>
       <c r="G10" s="51"/>
       <c r="H10" s="52">
         <f>SUMIF('Reimbursement details'!$G$32:$G52,"Inter-city travel",'Reimbursement details'!$L32:$L52)</f>
@@ -11672,7 +11663,7 @@
         <f>IFERROR(J10/$H$22*$J$22,0)</f>
         <v>532.32999999999993</v>
       </c>
-      <c r="L10" s="320"/>
+      <c r="L10" s="308"/>
     </row>
     <row r="11" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="49" t="s">
@@ -11682,9 +11673,9 @@
         <v>4</v>
       </c>
       <c r="C11" s="50"/>
-      <c r="D11" s="310"/>
-      <c r="E11" s="311"/>
-      <c r="F11" s="312"/>
+      <c r="D11" s="316"/>
+      <c r="E11" s="317"/>
+      <c r="F11" s="318"/>
       <c r="G11" s="51"/>
       <c r="H11" s="52">
         <f>SUMIF('Reimbursement details'!$G$32:$G52,"Travel to / from HK Airport",'Reimbursement details'!$L32:$L52)+SUMIF('Reimbursement details'!$G$32:$G52,"Travel to / from HK Port",'Reimbursement details'!$L32:$L52)</f>
@@ -11699,7 +11690,7 @@
         <f>IFERROR(J11/$H$22*$J$22,0)</f>
         <v>0</v>
       </c>
-      <c r="L11" s="321"/>
+      <c r="L11" s="309"/>
     </row>
     <row r="12" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="49" t="s">
@@ -11709,9 +11700,9 @@
         <v>4</v>
       </c>
       <c r="C12" s="50"/>
-      <c r="D12" s="310"/>
-      <c r="E12" s="311"/>
-      <c r="F12" s="312"/>
+      <c r="D12" s="316"/>
+      <c r="E12" s="317"/>
+      <c r="F12" s="318"/>
       <c r="G12" s="51"/>
       <c r="H12" s="141">
         <f>SUMIF('Reimbursement details'!$G$32:$G52,"Registration fee/ Course fee",'Reimbursement details'!L32:L52)</f>
@@ -11736,9 +11727,9 @@
         <v>4</v>
       </c>
       <c r="C13" s="50"/>
-      <c r="D13" s="310"/>
-      <c r="E13" s="311"/>
-      <c r="F13" s="312"/>
+      <c r="D13" s="316"/>
+      <c r="E13" s="317"/>
+      <c r="F13" s="318"/>
       <c r="G13" s="51"/>
       <c r="H13" s="52">
         <f>SUMIF('Reimbursement details'!$H$32:$H52,"*Visa*",'Reimbursement details'!$L32:$L52)</f>
@@ -11763,9 +11754,9 @@
         <v>4</v>
       </c>
       <c r="C14" s="50"/>
-      <c r="D14" s="310"/>
-      <c r="E14" s="311"/>
-      <c r="F14" s="312"/>
+      <c r="D14" s="316"/>
+      <c r="E14" s="317"/>
+      <c r="F14" s="318"/>
       <c r="G14" s="73"/>
       <c r="H14" s="52">
         <f>SUMIF('Reimbursement details'!$G$32:$G52,"Accommodation-Quarantine in Hong Kong",'Reimbursement details'!$L32:$L52)</f>
@@ -11787,9 +11778,9 @@
         <v>4</v>
       </c>
       <c r="C15" s="50"/>
-      <c r="D15" s="310"/>
-      <c r="E15" s="311"/>
-      <c r="F15" s="312"/>
+      <c r="D15" s="316"/>
+      <c r="E15" s="317"/>
+      <c r="F15" s="318"/>
       <c r="G15" s="73"/>
       <c r="H15" s="52">
         <f>SUMIF('Reimbursement details'!$G$32:$G52,"Others (Please specify)",'Reimbursement details'!L32:L52)-H13-H19</f>
@@ -11807,16 +11798,16 @@
       <c r="A16" s="49" t="s">
         <v>115</v>
       </c>
-      <c r="B16" s="307" t="s">
+      <c r="B16" s="321" t="s">
         <v>4</v>
       </c>
       <c r="C16" s="58" t="s">
         <v>116</v>
       </c>
-      <c r="D16" s="310"/>
-      <c r="E16" s="311"/>
-      <c r="F16" s="312"/>
-      <c r="G16" s="309"/>
+      <c r="D16" s="316"/>
+      <c r="E16" s="317"/>
+      <c r="F16" s="318"/>
+      <c r="G16" s="323"/>
       <c r="H16" s="145">
         <f>SUMIF('Reimbursement details'!$G$32:$G52,"Accommodation-Quarantine at destination",'Reimbursement details'!$L32:$L52)+SUMIF('Reimbursement details'!$G$32:$G52,"Accommodation",'Reimbursement details'!$L32:$L52)</f>
         <v>2815.25</v>
@@ -11830,21 +11821,21 @@
         <f>IFERROR(J16/$H$26*$J$26,0)</f>
         <v>2815.25</v>
       </c>
-      <c r="L16" s="324">
+      <c r="L16" s="312">
         <f>SUM(K16:K19)</f>
         <v>5311.3899999999994</v>
       </c>
     </row>
     <row r="17" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="38"/>
-      <c r="B17" s="307"/>
+      <c r="B17" s="321"/>
       <c r="C17" s="58" t="s">
         <v>117</v>
       </c>
-      <c r="D17" s="310"/>
-      <c r="E17" s="311"/>
-      <c r="F17" s="312"/>
-      <c r="G17" s="309"/>
+      <c r="D17" s="316"/>
+      <c r="E17" s="317"/>
+      <c r="F17" s="318"/>
+      <c r="G17" s="323"/>
       <c r="H17" s="146">
         <f>SUMIF('Reimbursement details'!$G$32:$G52,"Meals",'Reimbursement details'!$L32:$L52)</f>
         <v>2496.14</v>
@@ -11858,18 +11849,18 @@
         <f>IFERROR(J17/$H$26*$J$26,0)</f>
         <v>2496.14</v>
       </c>
-      <c r="L17" s="324"/>
+      <c r="L17" s="312"/>
     </row>
     <row r="18" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="38"/>
-      <c r="B18" s="307"/>
+      <c r="B18" s="321"/>
       <c r="C18" s="58" t="s">
         <v>118</v>
       </c>
-      <c r="D18" s="310"/>
-      <c r="E18" s="311"/>
-      <c r="F18" s="312"/>
-      <c r="G18" s="309"/>
+      <c r="D18" s="316"/>
+      <c r="E18" s="317"/>
+      <c r="F18" s="318"/>
+      <c r="G18" s="323"/>
       <c r="H18" s="71">
         <f>SUMIF('Reimbursement details'!$G$32:$G52,"Inner-city travel at destination",'Reimbursement details'!$L32:$L52)</f>
         <v>0</v>
@@ -11883,18 +11874,18 @@
         <f>IFERROR(J18/$H$26*$J$26,0)</f>
         <v>0</v>
       </c>
-      <c r="L18" s="324"/>
+      <c r="L18" s="312"/>
     </row>
     <row r="19" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="38"/>
-      <c r="B19" s="307"/>
+      <c r="B19" s="321"/>
       <c r="C19" s="58" t="s">
         <v>181</v>
       </c>
-      <c r="D19" s="308"/>
-      <c r="E19" s="308"/>
-      <c r="F19" s="308"/>
-      <c r="G19" s="309"/>
+      <c r="D19" s="322"/>
+      <c r="E19" s="322"/>
+      <c r="F19" s="322"/>
+      <c r="G19" s="323"/>
       <c r="H19" s="72">
         <f>SUMIF('Reimbursement details'!$H$32:$H52,"*SA",'Reimbursement details'!$L32:$L52)+SUMIF('Reimbursement details'!$H$32:$H52,"*subsistence",'Reimbursement details'!$L32:$L52)</f>
         <v>0</v>
@@ -11908,7 +11899,7 @@
         <f>IFERROR(J19/$H$26*$J$26,0)</f>
         <v>0</v>
       </c>
-      <c r="L19" s="324"/>
+      <c r="L19" s="312"/>
     </row>
     <row r="20" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="38"/>
@@ -12069,24 +12060,24 @@
       <c r="H29" s="35" t="s">
         <v>4</v>
       </c>
-      <c r="I29" s="313" t="s">
+      <c r="I29" s="324" t="s">
         <v>126</v>
       </c>
-      <c r="J29" s="313"/>
+      <c r="J29" s="324"/>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A30" s="65" t="s">
         <v>127</v>
       </c>
-      <c r="D30" s="314"/>
-      <c r="E30" s="314"/>
-      <c r="F30" s="314"/>
+      <c r="D30" s="319"/>
+      <c r="E30" s="319"/>
+      <c r="F30" s="319"/>
       <c r="G30" s="51" t="s">
         <v>111</v>
       </c>
       <c r="H30" s="66"/>
-      <c r="I30" s="315"/>
-      <c r="J30" s="315"/>
+      <c r="I30" s="320"/>
+      <c r="J30" s="320"/>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A31" s="38"/>
@@ -12137,17 +12128,11 @@
   </sheetData>
   <dataConsolidate/>
   <mergeCells count="23">
-    <mergeCell ref="L9:L11"/>
-    <mergeCell ref="H3:I3"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="H5:I5"/>
-    <mergeCell ref="L16:L19"/>
-    <mergeCell ref="B6:F6"/>
-    <mergeCell ref="D10:F10"/>
-    <mergeCell ref="D11:F11"/>
-    <mergeCell ref="D12:F12"/>
-    <mergeCell ref="D9:F9"/>
-    <mergeCell ref="D8:F8"/>
+    <mergeCell ref="B16:B19"/>
+    <mergeCell ref="D19:F19"/>
+    <mergeCell ref="G16:G19"/>
+    <mergeCell ref="D16:F16"/>
+    <mergeCell ref="I29:J29"/>
     <mergeCell ref="D30:F30"/>
     <mergeCell ref="I30:J30"/>
     <mergeCell ref="D14:F14"/>
@@ -12155,24 +12140,30 @@
     <mergeCell ref="D13:F13"/>
     <mergeCell ref="D17:F17"/>
     <mergeCell ref="D18:F18"/>
-    <mergeCell ref="B16:B19"/>
-    <mergeCell ref="D19:F19"/>
-    <mergeCell ref="G16:G19"/>
-    <mergeCell ref="D16:F16"/>
-    <mergeCell ref="I29:J29"/>
+    <mergeCell ref="B6:F6"/>
+    <mergeCell ref="D10:F10"/>
+    <mergeCell ref="D11:F11"/>
+    <mergeCell ref="D12:F12"/>
+    <mergeCell ref="D9:F9"/>
+    <mergeCell ref="D8:F8"/>
+    <mergeCell ref="L9:L11"/>
+    <mergeCell ref="H3:I3"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="H5:I5"/>
+    <mergeCell ref="L16:L19"/>
   </mergeCells>
   <conditionalFormatting sqref="H9:H19">
-    <cfRule type="expression" dxfId="4" priority="2">
+    <cfRule type="expression" dxfId="2" priority="2">
       <formula>INDIRECT("RC",FALSE)&lt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J9:J19">
-    <cfRule type="expression" dxfId="3" priority="1">
+    <cfRule type="expression" dxfId="1" priority="1">
       <formula>INDIRECT("RC",FALSE)&lt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L20">
-    <cfRule type="cellIs" dxfId="2" priority="3" operator="notEqual">
+    <cfRule type="cellIs" dxfId="0" priority="3" operator="notEqual">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
